--- a/final_data_pipeline/output/325180_elec_options.xlsx
+++ b/final_data_pipeline/output/325180_elec_options.xlsx
@@ -4366,7 +4366,7 @@
         <v>224</v>
       </c>
       <c r="AD34">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AE34">
         <v>8000</v>
@@ -4464,7 +4464,7 @@
         <v>223</v>
       </c>
       <c r="AD35">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AE35">
         <v>8000</v>
@@ -4559,7 +4559,7 @@
         <v>224</v>
       </c>
       <c r="AD36">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AE36">
         <v>8000</v>
@@ -4657,7 +4657,7 @@
         <v>223</v>
       </c>
       <c r="AD37">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AE37">
         <v>8000</v>
@@ -6308,7 +6308,7 @@
         <v>224</v>
       </c>
       <c r="AD54">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE54">
         <v>8000</v>
@@ -6403,7 +6403,7 @@
         <v>224</v>
       </c>
       <c r="AD55">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE55">
         <v>8000</v>
@@ -6501,7 +6501,7 @@
         <v>224</v>
       </c>
       <c r="AD56">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE56">
         <v>8000</v>
@@ -6599,7 +6599,7 @@
         <v>223</v>
       </c>
       <c r="AD57">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE57">
         <v>8000</v>
@@ -6697,7 +6697,7 @@
         <v>223</v>
       </c>
       <c r="AD58">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE58">
         <v>8000</v>
@@ -6795,7 +6795,7 @@
         <v>223</v>
       </c>
       <c r="AD59">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE59">
         <v>8000</v>
@@ -6893,7 +6893,7 @@
         <v>223</v>
       </c>
       <c r="AD60">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE60">
         <v>8000</v>
@@ -6991,7 +6991,7 @@
         <v>224</v>
       </c>
       <c r="AD61">
-        <v>10</v>
+        <v>12.93898809523811</v>
       </c>
       <c r="AE61">
         <v>8000</v>
@@ -7867,7 +7867,7 @@
         <v>224</v>
       </c>
       <c r="AD70">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE70">
         <v>8000</v>
@@ -7962,7 +7962,7 @@
         <v>224</v>
       </c>
       <c r="AD71">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE71">
         <v>8000</v>
@@ -8060,7 +8060,7 @@
         <v>223</v>
       </c>
       <c r="AD72">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE72">
         <v>8000</v>
@@ -8158,7 +8158,7 @@
         <v>223</v>
       </c>
       <c r="AD73">
-        <v>10</v>
+        <v>13.46442495126706</v>
       </c>
       <c r="AE73">
         <v>8000</v>
@@ -8256,7 +8256,7 @@
         <v>224</v>
       </c>
       <c r="AD74">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE74">
         <v>8000</v>
@@ -8354,7 +8354,7 @@
         <v>223</v>
       </c>
       <c r="AD75">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE75">
         <v>8000</v>
@@ -8449,7 +8449,7 @@
         <v>224</v>
       </c>
       <c r="AD76">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE76">
         <v>8000</v>
@@ -8547,7 +8547,7 @@
         <v>223</v>
       </c>
       <c r="AD77">
-        <v>10</v>
+        <v>15.74228395061728</v>
       </c>
       <c r="AE77">
         <v>8000</v>
@@ -10979,7 +10979,7 @@
         <v>224</v>
       </c>
       <c r="AD102">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE102">
         <v>8000</v>
@@ -11074,7 +11074,7 @@
         <v>224</v>
       </c>
       <c r="AD103">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE103">
         <v>8000</v>
@@ -11172,7 +11172,7 @@
         <v>223</v>
       </c>
       <c r="AD104">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE104">
         <v>8000</v>
@@ -11270,7 +11270,7 @@
         <v>223</v>
       </c>
       <c r="AD105">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE105">
         <v>8000</v>
@@ -12146,7 +12146,7 @@
         <v>223</v>
       </c>
       <c r="AD114">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="AE114">
         <v>8000</v>
@@ -12241,7 +12241,7 @@
         <v>224</v>
       </c>
       <c r="AD115">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="AE115">
         <v>8000</v>
@@ -12339,7 +12339,7 @@
         <v>223</v>
       </c>
       <c r="AD116">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="AE116">
         <v>8000</v>
@@ -12437,7 +12437,7 @@
         <v>224</v>
       </c>
       <c r="AD117">
-        <v>10</v>
+        <v>20.68981481481483</v>
       </c>
       <c r="AE117">
         <v>8000</v>
@@ -14866,7 +14866,7 @@
         <v>224</v>
       </c>
       <c r="AD142">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE142">
         <v>8000</v>
@@ -14961,7 +14961,7 @@
         <v>224</v>
       </c>
       <c r="AD143">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE143">
         <v>8000</v>
@@ -15059,7 +15059,7 @@
         <v>224</v>
       </c>
       <c r="AD144">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE144">
         <v>8000</v>
@@ -15157,7 +15157,7 @@
         <v>223</v>
       </c>
       <c r="AD145">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE145">
         <v>8000</v>
@@ -15255,7 +15255,7 @@
         <v>224</v>
       </c>
       <c r="AD146">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE146">
         <v>8000</v>
@@ -15353,7 +15353,7 @@
         <v>223</v>
       </c>
       <c r="AD147">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE147">
         <v>8000</v>
@@ -15451,7 +15451,7 @@
         <v>223</v>
       </c>
       <c r="AD148">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE148">
         <v>8000</v>
@@ -15549,7 +15549,7 @@
         <v>223</v>
       </c>
       <c r="AD149">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE149">
         <v>8000</v>
@@ -15647,7 +15647,7 @@
         <v>223</v>
       </c>
       <c r="AD150">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE150">
         <v>8000</v>
@@ -15745,7 +15745,7 @@
         <v>223</v>
       </c>
       <c r="AD151">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE151">
         <v>8000</v>
@@ -15840,7 +15840,7 @@
         <v>224</v>
       </c>
       <c r="AD152">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE152">
         <v>8000</v>
@@ -15938,7 +15938,7 @@
         <v>224</v>
       </c>
       <c r="AD153">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE153">
         <v>8000</v>
@@ -16033,7 +16033,7 @@
         <v>224</v>
       </c>
       <c r="AD154">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE154">
         <v>8000</v>
@@ -16131,7 +16131,7 @@
         <v>223</v>
       </c>
       <c r="AD155">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE155">
         <v>8000</v>
@@ -16229,7 +16229,7 @@
         <v>224</v>
       </c>
       <c r="AD156">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE156">
         <v>8000</v>
@@ -16327,7 +16327,7 @@
         <v>223</v>
       </c>
       <c r="AD157">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AE157">
         <v>8000</v>
@@ -16814,7 +16814,7 @@
         <v>224</v>
       </c>
       <c r="AD162">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE162">
         <v>8000</v>
@@ -16909,7 +16909,7 @@
         <v>224</v>
       </c>
       <c r="AD163">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE163">
         <v>8000</v>
@@ -17007,7 +17007,7 @@
         <v>223</v>
       </c>
       <c r="AD164">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE164">
         <v>8000</v>
@@ -17105,7 +17105,7 @@
         <v>223</v>
       </c>
       <c r="AD165">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AE165">
         <v>8000</v>
@@ -19537,7 +19537,7 @@
         <v>223</v>
       </c>
       <c r="AD190">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AE190">
         <v>8000</v>
@@ -19635,7 +19635,7 @@
         <v>223</v>
       </c>
       <c r="AD191">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AE191">
         <v>8000</v>
@@ -19733,7 +19733,7 @@
         <v>224</v>
       </c>
       <c r="AD192">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AE192">
         <v>8000</v>
@@ -19828,7 +19828,7 @@
         <v>224</v>
       </c>
       <c r="AD193">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AE193">
         <v>8000</v>
@@ -20312,7 +20312,7 @@
         <v>224</v>
       </c>
       <c r="AD198">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE198">
         <v>8000</v>
@@ -20410,7 +20410,7 @@
         <v>223</v>
       </c>
       <c r="AD199">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE199">
         <v>8000</v>
@@ -20508,7 +20508,7 @@
         <v>223</v>
       </c>
       <c r="AD200">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE200">
         <v>8000</v>
@@ -20606,7 +20606,7 @@
         <v>224</v>
       </c>
       <c r="AD201">
-        <v>10</v>
+        <v>19.79629629629628</v>
       </c>
       <c r="AE201">
         <v>8000</v>
@@ -20707,7 +20707,7 @@
         <v>224</v>
       </c>
       <c r="AD202">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE202">
         <v>8000</v>
@@ -20805,7 +20805,7 @@
         <v>223</v>
       </c>
       <c r="AD203">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE203">
         <v>8000</v>
@@ -20900,7 +20900,7 @@
         <v>224</v>
       </c>
       <c r="AD204">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE204">
         <v>8000</v>
@@ -20998,7 +20998,7 @@
         <v>223</v>
       </c>
       <c r="AD205">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE205">
         <v>8000</v>
@@ -21093,7 +21093,7 @@
         <v>224</v>
       </c>
       <c r="AD206">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE206">
         <v>8000</v>
@@ -21191,7 +21191,7 @@
         <v>223</v>
       </c>
       <c r="AD207">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE207">
         <v>8000</v>
@@ -21289,7 +21289,7 @@
         <v>223</v>
       </c>
       <c r="AD208">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE208">
         <v>8000</v>
@@ -21387,7 +21387,7 @@
         <v>224</v>
       </c>
       <c r="AD209">
-        <v>10</v>
+        <v>19.30324074074072</v>
       </c>
       <c r="AE209">
         <v>8000</v>
@@ -21485,7 +21485,7 @@
         <v>224</v>
       </c>
       <c r="AD210">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE210">
         <v>8000</v>
@@ -21583,7 +21583,7 @@
         <v>224</v>
       </c>
       <c r="AD211">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE211">
         <v>8000</v>
@@ -21681,7 +21681,7 @@
         <v>224</v>
       </c>
       <c r="AD212">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE212">
         <v>8000</v>
@@ -21779,7 +21779,7 @@
         <v>224</v>
       </c>
       <c r="AD213">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE213">
         <v>8000</v>
@@ -21877,7 +21877,7 @@
         <v>224</v>
       </c>
       <c r="AD214">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE214">
         <v>8000</v>
@@ -21975,7 +21975,7 @@
         <v>224</v>
       </c>
       <c r="AD215">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE215">
         <v>8000</v>
@@ -22073,7 +22073,7 @@
         <v>224</v>
       </c>
       <c r="AD216">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE216">
         <v>8000</v>
@@ -22171,7 +22171,7 @@
         <v>224</v>
       </c>
       <c r="AD217">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE217">
         <v>8000</v>
@@ -22269,7 +22269,7 @@
         <v>224</v>
       </c>
       <c r="AD218">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE218">
         <v>8000</v>
@@ -22367,7 +22367,7 @@
         <v>223</v>
       </c>
       <c r="AD219">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE219">
         <v>8000</v>
@@ -22465,7 +22465,7 @@
         <v>223</v>
       </c>
       <c r="AD220">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE220">
         <v>8000</v>
@@ -22563,7 +22563,7 @@
         <v>223</v>
       </c>
       <c r="AD221">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE221">
         <v>8000</v>
@@ -22661,7 +22661,7 @@
         <v>223</v>
       </c>
       <c r="AD222">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE222">
         <v>8000</v>
@@ -22759,7 +22759,7 @@
         <v>223</v>
       </c>
       <c r="AD223">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE223">
         <v>8000</v>
@@ -22857,7 +22857,7 @@
         <v>223</v>
       </c>
       <c r="AD224">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE224">
         <v>8000</v>
@@ -22955,7 +22955,7 @@
         <v>223</v>
       </c>
       <c r="AD225">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE225">
         <v>8000</v>
@@ -23053,7 +23053,7 @@
         <v>223</v>
       </c>
       <c r="AD226">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE226">
         <v>8000</v>
@@ -23151,7 +23151,7 @@
         <v>223</v>
       </c>
       <c r="AD227">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE227">
         <v>8000</v>
@@ -23249,7 +23249,7 @@
         <v>223</v>
       </c>
       <c r="AD228">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE228">
         <v>8000</v>
@@ -23347,7 +23347,7 @@
         <v>223</v>
       </c>
       <c r="AD229">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE229">
         <v>8000</v>
@@ -23445,7 +23445,7 @@
         <v>223</v>
       </c>
       <c r="AD230">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE230">
         <v>8000</v>
@@ -23543,7 +23543,7 @@
         <v>224</v>
       </c>
       <c r="AD231">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE231">
         <v>8000</v>
@@ -23641,7 +23641,7 @@
         <v>224</v>
       </c>
       <c r="AD232">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE232">
         <v>8000</v>
@@ -23739,7 +23739,7 @@
         <v>224</v>
       </c>
       <c r="AD233">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE233">
         <v>8000</v>
@@ -23837,7 +23837,7 @@
         <v>223</v>
       </c>
       <c r="AD234">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE234">
         <v>8000</v>
@@ -23932,7 +23932,7 @@
         <v>224</v>
       </c>
       <c r="AD235">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE235">
         <v>8000</v>
@@ -24027,7 +24027,7 @@
         <v>224</v>
       </c>
       <c r="AD236">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE236">
         <v>8000</v>
@@ -24122,7 +24122,7 @@
         <v>224</v>
       </c>
       <c r="AD237">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE237">
         <v>8000</v>
@@ -24217,7 +24217,7 @@
         <v>224</v>
       </c>
       <c r="AD238">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE238">
         <v>8000</v>
@@ -24312,7 +24312,7 @@
         <v>224</v>
       </c>
       <c r="AD239">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE239">
         <v>8000</v>
@@ -24407,7 +24407,7 @@
         <v>224</v>
       </c>
       <c r="AD240">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE240">
         <v>8000</v>
@@ -24505,7 +24505,7 @@
         <v>223</v>
       </c>
       <c r="AD241">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE241">
         <v>8000</v>
@@ -24603,7 +24603,7 @@
         <v>223</v>
       </c>
       <c r="AD242">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE242">
         <v>8000</v>
@@ -24701,7 +24701,7 @@
         <v>223</v>
       </c>
       <c r="AD243">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE243">
         <v>8000</v>
@@ -24796,7 +24796,7 @@
         <v>224</v>
       </c>
       <c r="AD244">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE244">
         <v>8000</v>
@@ -24894,7 +24894,7 @@
         <v>223</v>
       </c>
       <c r="AD245">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE245">
         <v>8000</v>
@@ -24992,7 +24992,7 @@
         <v>223</v>
       </c>
       <c r="AD246">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE246">
         <v>8000</v>
@@ -25090,7 +25090,7 @@
         <v>223</v>
       </c>
       <c r="AD247">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE247">
         <v>8000</v>
@@ -25188,7 +25188,7 @@
         <v>223</v>
       </c>
       <c r="AD248">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE248">
         <v>8000</v>
@@ -25286,7 +25286,7 @@
         <v>223</v>
       </c>
       <c r="AD249">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE249">
         <v>8000</v>
@@ -25384,7 +25384,7 @@
         <v>223</v>
       </c>
       <c r="AD250">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE250">
         <v>8000</v>
@@ -25482,7 +25482,7 @@
         <v>223</v>
       </c>
       <c r="AD251">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE251">
         <v>8000</v>
@@ -25577,7 +25577,7 @@
         <v>224</v>
       </c>
       <c r="AD252">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE252">
         <v>8000</v>
@@ -25672,7 +25672,7 @@
         <v>224</v>
       </c>
       <c r="AD253">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE253">
         <v>8000</v>
@@ -25767,7 +25767,7 @@
         <v>224</v>
       </c>
       <c r="AD254">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE254">
         <v>8000</v>
@@ -25862,7 +25862,7 @@
         <v>224</v>
       </c>
       <c r="AD255">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE255">
         <v>8000</v>
@@ -25960,7 +25960,7 @@
         <v>223</v>
       </c>
       <c r="AD256">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE256">
         <v>8000</v>
@@ -26055,7 +26055,7 @@
         <v>224</v>
       </c>
       <c r="AD257">
-        <v>10</v>
+        <v>13.00385802469133</v>
       </c>
       <c r="AE257">
         <v>8000</v>
@@ -26539,7 +26539,7 @@
         <v>224</v>
       </c>
       <c r="AD262">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AE262">
         <v>8000</v>
@@ -26637,7 +26637,7 @@
         <v>224</v>
       </c>
       <c r="AD263">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AE263">
         <v>8000</v>
@@ -26735,7 +26735,7 @@
         <v>223</v>
       </c>
       <c r="AD264">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AE264">
         <v>8000</v>
@@ -26833,7 +26833,7 @@
         <v>223</v>
       </c>
       <c r="AD265">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AE265">
         <v>8000</v>
@@ -26931,7 +26931,7 @@
         <v>224</v>
       </c>
       <c r="AD266">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE266">
         <v>8000</v>
@@ -27026,7 +27026,7 @@
         <v>224</v>
       </c>
       <c r="AD267">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE267">
         <v>8000</v>
@@ -27124,7 +27124,7 @@
         <v>223</v>
       </c>
       <c r="AD268">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE268">
         <v>8000</v>
@@ -27222,7 +27222,7 @@
         <v>223</v>
       </c>
       <c r="AD269">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE269">
         <v>8000</v>
@@ -32377,7 +32377,7 @@
         <v>224</v>
       </c>
       <c r="AD322">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AE322">
         <v>8000</v>
@@ -32475,7 +32475,7 @@
         <v>223</v>
       </c>
       <c r="AD323">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AE323">
         <v>8000</v>
@@ -32573,7 +32573,7 @@
         <v>223</v>
       </c>
       <c r="AD324">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AE324">
         <v>8000</v>
@@ -32668,7 +32668,7 @@
         <v>224</v>
       </c>
       <c r="AD325">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AE325">
         <v>8000</v>
@@ -32766,7 +32766,7 @@
         <v>224</v>
       </c>
       <c r="AD326">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="AE326">
         <v>8000</v>
@@ -32861,7 +32861,7 @@
         <v>224</v>
       </c>
       <c r="AD327">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="AE327">
         <v>8000</v>
@@ -32959,7 +32959,7 @@
         <v>223</v>
       </c>
       <c r="AD328">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="AE328">
         <v>8000</v>
@@ -33057,7 +33057,7 @@
         <v>223</v>
       </c>
       <c r="AD329">
-        <v>10</v>
+        <v>5.486111111111112</v>
       </c>
       <c r="AE329">
         <v>8000</v>
@@ -33155,7 +33155,7 @@
         <v>223</v>
       </c>
       <c r="AD330">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE330">
         <v>8000</v>
@@ -33253,7 +33253,7 @@
         <v>224</v>
       </c>
       <c r="AD331">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE331">
         <v>8000</v>
@@ -33351,7 +33351,7 @@
         <v>224</v>
       </c>
       <c r="AD332">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE332">
         <v>8000</v>
@@ -33446,7 +33446,7 @@
         <v>224</v>
       </c>
       <c r="AD333">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE333">
         <v>8000</v>
@@ -33541,7 +33541,7 @@
         <v>224</v>
       </c>
       <c r="AD334">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE334">
         <v>8000</v>
@@ -33636,7 +33636,7 @@
         <v>224</v>
       </c>
       <c r="AD335">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE335">
         <v>8000</v>
@@ -33734,7 +33734,7 @@
         <v>223</v>
       </c>
       <c r="AD336">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE336">
         <v>8000</v>
@@ -33832,7 +33832,7 @@
         <v>223</v>
       </c>
       <c r="AD337">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE337">
         <v>8000</v>
@@ -33930,7 +33930,7 @@
         <v>224</v>
       </c>
       <c r="AD338">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE338">
         <v>8000</v>
@@ -34028,7 +34028,7 @@
         <v>223</v>
       </c>
       <c r="AD339">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE339">
         <v>8000</v>
@@ -34126,7 +34126,7 @@
         <v>223</v>
       </c>
       <c r="AD340">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE340">
         <v>8000</v>
@@ -34221,7 +34221,7 @@
         <v>224</v>
       </c>
       <c r="AD341">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE341">
         <v>8000</v>
@@ -34319,7 +34319,7 @@
         <v>224</v>
       </c>
       <c r="AD342">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE342">
         <v>8000</v>
@@ -34414,7 +34414,7 @@
         <v>224</v>
       </c>
       <c r="AD343">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE343">
         <v>8000</v>
@@ -34512,7 +34512,7 @@
         <v>223</v>
       </c>
       <c r="AD344">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE344">
         <v>8000</v>
@@ -34610,7 +34610,7 @@
         <v>223</v>
       </c>
       <c r="AD345">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE345">
         <v>8000</v>
@@ -34708,7 +34708,7 @@
         <v>223</v>
       </c>
       <c r="AD346">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE346">
         <v>8000</v>
@@ -34806,7 +34806,7 @@
         <v>223</v>
       </c>
       <c r="AD347">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE347">
         <v>8000</v>
@@ -34904,7 +34904,7 @@
         <v>223</v>
       </c>
       <c r="AD348">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE348">
         <v>8000</v>
@@ -35002,7 +35002,7 @@
         <v>224</v>
       </c>
       <c r="AD349">
-        <v>10</v>
+        <v>1.925925925925943</v>
       </c>
       <c r="AE349">
         <v>8000</v>
@@ -37434,7 +37434,7 @@
         <v>224</v>
       </c>
       <c r="AD374">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE374">
         <v>8000</v>
@@ -37532,7 +37532,7 @@
         <v>223</v>
       </c>
       <c r="AD375">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE375">
         <v>8000</v>
@@ -37630,7 +37630,7 @@
         <v>223</v>
       </c>
       <c r="AD376">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE376">
         <v>8000</v>
@@ -37725,7 +37725,7 @@
         <v>224</v>
       </c>
       <c r="AD377">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE377">
         <v>8000</v>
@@ -37823,7 +37823,7 @@
         <v>223</v>
       </c>
       <c r="AD378">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE378">
         <v>8000</v>
@@ -37921,7 +37921,7 @@
         <v>223</v>
       </c>
       <c r="AD379">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE379">
         <v>8000</v>
@@ -38019,7 +38019,7 @@
         <v>224</v>
       </c>
       <c r="AD380">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE380">
         <v>8000</v>
@@ -38114,7 +38114,7 @@
         <v>224</v>
       </c>
       <c r="AD381">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AE381">
         <v>8000</v>
@@ -38209,7 +38209,7 @@
         <v>224</v>
       </c>
       <c r="AD382">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AE382">
         <v>8000</v>
@@ -38307,7 +38307,7 @@
         <v>223</v>
       </c>
       <c r="AD383">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AE383">
         <v>8000</v>
@@ -38405,7 +38405,7 @@
         <v>224</v>
       </c>
       <c r="AD384">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AE384">
         <v>8000</v>
@@ -38503,7 +38503,7 @@
         <v>223</v>
       </c>
       <c r="AD385">
-        <v>10</v>
+        <v>13.62268518518517</v>
       </c>
       <c r="AE385">
         <v>8000</v>
@@ -40154,7 +40154,7 @@
         <v>224</v>
       </c>
       <c r="AD402">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE402">
         <v>8000</v>
@@ -40252,7 +40252,7 @@
         <v>223</v>
       </c>
       <c r="AD403">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE403">
         <v>8000</v>
@@ -40350,7 +40350,7 @@
         <v>223</v>
       </c>
       <c r="AD404">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE404">
         <v>8000</v>
@@ -40448,7 +40448,7 @@
         <v>224</v>
       </c>
       <c r="AD405">
-        <v>10</v>
+        <v>1.791666666666668</v>
       </c>
       <c r="AE405">
         <v>8000</v>
@@ -40543,7 +40543,7 @@
         <v>224</v>
       </c>
       <c r="AD406">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AE406">
         <v>8000</v>
@@ -40641,7 +40641,7 @@
         <v>224</v>
       </c>
       <c r="AD407">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AE407">
         <v>8000</v>
@@ -40739,7 +40739,7 @@
         <v>223</v>
       </c>
       <c r="AD408">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AE408">
         <v>8000</v>
@@ -40837,7 +40837,7 @@
         <v>223</v>
       </c>
       <c r="AD409">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AE409">
         <v>8000</v>
@@ -40935,7 +40935,7 @@
         <v>223</v>
       </c>
       <c r="AD410">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AE410">
         <v>8000</v>
@@ -41033,7 +41033,7 @@
         <v>223</v>
       </c>
       <c r="AD411">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AE411">
         <v>8000</v>
@@ -41131,7 +41131,7 @@
         <v>223</v>
       </c>
       <c r="AD412">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AE412">
         <v>8000</v>
@@ -41229,7 +41229,7 @@
         <v>223</v>
       </c>
       <c r="AD413">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AE413">
         <v>8000</v>
@@ -41327,7 +41327,7 @@
         <v>223</v>
       </c>
       <c r="AD414">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AE414">
         <v>8000</v>
@@ -41425,7 +41425,7 @@
         <v>224</v>
       </c>
       <c r="AD415">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AE415">
         <v>8000</v>
@@ -41523,7 +41523,7 @@
         <v>224</v>
       </c>
       <c r="AD416">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AE416">
         <v>8000</v>
@@ -41621,7 +41621,7 @@
         <v>224</v>
       </c>
       <c r="AD417">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AE417">
         <v>8000</v>
@@ -41716,7 +41716,7 @@
         <v>224</v>
       </c>
       <c r="AD418">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AE418">
         <v>8000</v>
@@ -41811,7 +41811,7 @@
         <v>224</v>
       </c>
       <c r="AD419">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AE419">
         <v>8000</v>
@@ -41906,7 +41906,7 @@
         <v>224</v>
       </c>
       <c r="AD420">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AE420">
         <v>8000</v>
@@ -42001,7 +42001,7 @@
         <v>224</v>
       </c>
       <c r="AD421">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AE421">
         <v>8000</v>
@@ -42096,7 +42096,7 @@
         <v>224</v>
       </c>
       <c r="AD422">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AE422">
         <v>8000</v>
@@ -42194,7 +42194,7 @@
         <v>224</v>
       </c>
       <c r="AD423">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AE423">
         <v>8000</v>
@@ -42292,7 +42292,7 @@
         <v>224</v>
       </c>
       <c r="AD424">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AE424">
         <v>8000</v>
@@ -42390,7 +42390,7 @@
         <v>223</v>
       </c>
       <c r="AD425">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AE425">
         <v>8000</v>
@@ -42488,7 +42488,7 @@
         <v>223</v>
       </c>
       <c r="AD426">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AE426">
         <v>8000</v>
@@ -42586,7 +42586,7 @@
         <v>223</v>
       </c>
       <c r="AD427">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AE427">
         <v>8000</v>
@@ -42684,7 +42684,7 @@
         <v>223</v>
       </c>
       <c r="AD428">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AE428">
         <v>8000</v>
@@ -42782,7 +42782,7 @@
         <v>223</v>
       </c>
       <c r="AD429">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AE429">
         <v>8000</v>
@@ -42880,7 +42880,7 @@
         <v>223</v>
       </c>
       <c r="AD430">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AE430">
         <v>8000</v>
@@ -42975,7 +42975,7 @@
         <v>224</v>
       </c>
       <c r="AD431">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AE431">
         <v>8000</v>
@@ -43073,7 +43073,7 @@
         <v>223</v>
       </c>
       <c r="AD432">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AE432">
         <v>8000</v>
@@ -43171,7 +43171,7 @@
         <v>224</v>
       </c>
       <c r="AD433">
-        <v>10</v>
+        <v>21.19907407407406</v>
       </c>
       <c r="AE433">
         <v>8000</v>
